--- a/artfynd/A 57047-2025 artfynd.xlsx
+++ b/artfynd/A 57047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117215255</v>
+        <v>117215178</v>
       </c>
       <c r="B2" t="n">
-        <v>78446</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560095</v>
+        <v>560027</v>
       </c>
       <c r="R2" t="n">
-        <v>7073296</v>
+        <v>7073447</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117215371</v>
+        <v>117215199</v>
       </c>
       <c r="B3" t="n">
-        <v>74558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560016</v>
+        <v>560003</v>
       </c>
       <c r="R3" t="n">
-        <v>7073587</v>
+        <v>7073416</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117215199</v>
+        <v>117215244</v>
       </c>
       <c r="B4" t="n">
-        <v>82225</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560003</v>
+        <v>560091</v>
       </c>
       <c r="R4" t="n">
-        <v>7073416</v>
+        <v>7073294</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117215317</v>
+        <v>117215361</v>
       </c>
       <c r="B5" t="n">
-        <v>78446</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560037</v>
+        <v>560029</v>
       </c>
       <c r="R5" t="n">
-        <v>7073184</v>
+        <v>7073599</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117215361</v>
+        <v>117215255</v>
       </c>
       <c r="B6" t="n">
-        <v>82225</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560029</v>
+        <v>560095</v>
       </c>
       <c r="R6" t="n">
-        <v>7073599</v>
+        <v>7073296</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117215276</v>
+        <v>117215292</v>
       </c>
       <c r="B7" t="n">
-        <v>90483</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560190</v>
+        <v>560217</v>
       </c>
       <c r="R7" t="n">
-        <v>7073225</v>
+        <v>7073135</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117215178</v>
+        <v>117215317</v>
       </c>
       <c r="B8" t="n">
-        <v>90461</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560027</v>
+        <v>560037</v>
       </c>
       <c r="R8" t="n">
-        <v>7073447</v>
+        <v>7073184</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117215214</v>
+        <v>117215371</v>
       </c>
       <c r="B9" t="n">
-        <v>90483</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560017</v>
+        <v>560016</v>
       </c>
       <c r="R9" t="n">
-        <v>7073396</v>
+        <v>7073587</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1520,218 +1480,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>117215292</v>
-      </c>
-      <c r="B10" t="n">
-        <v>78446</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Moggsjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>560217</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7073135</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>117215244</v>
-      </c>
-      <c r="B11" t="n">
-        <v>82225</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Moggsjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>560091</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7073294</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57047-2025 artfynd.xlsx
+++ b/artfynd/A 57047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215178</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215199</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215361</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215292</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215317</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,8 +1520,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117215371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>